--- a/Herman_sim/bachelor_montecarlo/transportmodell.xlsx
+++ b/Herman_sim/bachelor_montecarlo/transportmodell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/hermaose_ntnu_no/Documents/Programmering Bachelor/Transport-under-usikkerhet---Monte-Carlo/Herman_sim/bachelor_montecarlo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{5AC497FB-2049-4AA6-91D9-3C030F7F39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C37E367-5950-41CC-8737-26D818D22582}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{5AC497FB-2049-4AA6-91D9-3C030F7F39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{134D378E-3566-4F73-8050-D570C1F6EE53}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="177">
   <si>
     <t>RuteID</t>
   </si>
@@ -285,28 +285,16 @@
     <t>RoRo short-sea Nordsjøen; værforsinkelser</t>
   </si>
   <si>
-    <t>Andersson et al. (2017); bransjenorm</t>
-  </si>
-  <si>
     <t>Sjø_havgaaende</t>
   </si>
   <si>
     <t>Lengre havreise (R5: Rotterdam-Bar); mer væreksp.</t>
   </si>
   <si>
-    <t>Andersson et al. (2017)</t>
-  </si>
-  <si>
     <t>Generisk jernbane (R2-R4)</t>
   </si>
   <si>
-    <t>Demiridis &amp; Pyrgidis (2022)</t>
-  </si>
-  <si>
     <t>Lastebil; mest forutsigbar mode</t>
-  </si>
-  <si>
-    <t>de Jong (2014); Janic (2007)</t>
   </si>
   <si>
     <t>2. Terminaltid pr modus — Triangulær(min, mode, max) i timer</t>
@@ -677,7 +665,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -747,6 +735,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -831,7 +825,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -883,15 +877,14 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -966,6 +959,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5654,7 +5650,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="8.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -5665,22 +5661,22 @@
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="37" t="s">
         <v>4</v>
       </c>
@@ -5693,11 +5689,9 @@
       <c r="D5" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="38" t="s">
         <v>20</v>
       </c>
@@ -5710,13 +5704,11 @@
       <c r="D6" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="38" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>79</v>
@@ -5725,13 +5717,11 @@
         <v>0.15</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>82</v>
+      </c>
+      <c r="E7" s="38"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="38" t="s">
         <v>39</v>
       </c>
@@ -5742,13 +5732,11 @@
         <v>0.2</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+      <c r="E8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="38" t="s">
         <v>26</v>
       </c>
@@ -5759,31 +5747,31 @@
         <v>0.08</v>
       </c>
       <c r="D9" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="38"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I11" s="50"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="C13" s="37" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
+      <c r="D13" s="37" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>93</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>77</v>
@@ -5792,7 +5780,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="38" t="s">
         <v>20</v>
       </c>
@@ -5806,15 +5794,15 @@
         <v>24</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="40">
         <v>8</v>
@@ -5826,13 +5814,13 @@
         <v>24</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="38" t="s">
         <v>39</v>
       </c>
@@ -5846,10 +5834,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -5866,22 +5854,22 @@
         <v>8</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -5889,10 +5877,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>78</v>
@@ -5906,24 +5894,24 @@
         <v>68</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="40">
         <v>68</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -5934,10 +5922,10 @@
         <v>48</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -5948,31 +5936,31 @@
         <v>0</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="41" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>77</v>
@@ -5983,261 +5971,261 @@
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="48">
+        <v>111</v>
+      </c>
+      <c r="B31" s="45">
         <v>0.25</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="45">
         <v>0.5</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="45">
         <v>1</v>
       </c>
-      <c r="E31" s="49" t="s">
-        <v>116</v>
+      <c r="E31" s="38" t="s">
+        <v>112</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="48">
+        <v>114</v>
+      </c>
+      <c r="B32" s="45">
         <v>0.5</v>
       </c>
-      <c r="C32" s="48">
+      <c r="C32" s="45">
         <v>1.5</v>
       </c>
-      <c r="D32" s="48">
+      <c r="D32" s="45">
         <v>3</v>
       </c>
-      <c r="E32" s="49" t="s">
-        <v>119</v>
+      <c r="E32" s="38" t="s">
+        <v>115</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="48">
+        <v>117</v>
+      </c>
+      <c r="B33" s="45">
         <v>1</v>
       </c>
-      <c r="C33" s="48">
+      <c r="C33" s="45">
         <v>1.5</v>
       </c>
-      <c r="D33" s="48">
+      <c r="D33" s="45">
         <v>3</v>
       </c>
-      <c r="E33" s="49" t="s">
-        <v>122</v>
+      <c r="E33" s="38" t="s">
+        <v>118</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="50">
+        <v>120</v>
+      </c>
+      <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34" s="50">
+      <c r="C34">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D34" s="50">
+      <c r="D34">
         <v>8</v>
       </c>
-      <c r="E34" s="50" t="s">
-        <v>125</v>
+      <c r="E34" t="s">
+        <v>121</v>
       </c>
       <c r="F34" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>127</v>
-      </c>
-      <c r="B35" s="50">
+        <v>123</v>
+      </c>
+      <c r="B35">
         <v>0.5</v>
       </c>
-      <c r="C35" s="50">
+      <c r="C35">
         <v>1</v>
       </c>
-      <c r="D35" s="50">
+      <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="50" t="s">
-        <v>128</v>
+      <c r="E35" t="s">
+        <v>124</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B36" s="50">
+        <v>126</v>
+      </c>
+      <c r="B36">
         <v>0.5</v>
       </c>
-      <c r="C36" s="50">
+      <c r="C36">
         <v>1</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36">
         <v>2</v>
       </c>
-      <c r="E36" s="50" t="s">
-        <v>131</v>
+      <c r="E36" t="s">
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="50">
+        <v>128</v>
+      </c>
+      <c r="B37">
         <v>0.25</v>
       </c>
-      <c r="C37" s="50">
+      <c r="C37">
         <v>0.5</v>
       </c>
-      <c r="D37" s="50">
+      <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" s="50" t="s">
-        <v>133</v>
+      <c r="E37" t="s">
+        <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="B38" s="50">
+      <c r="A38" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38">
         <v>0.25</v>
       </c>
-      <c r="C38" s="50">
+      <c r="C38">
         <v>0.5</v>
       </c>
-      <c r="D38" s="50">
+      <c r="D38">
         <v>1</v>
       </c>
-      <c r="E38" s="50" t="s">
-        <v>135</v>
+      <c r="E38" t="s">
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="48">
+        <v>132</v>
+      </c>
+      <c r="B39" s="45">
         <v>0.25</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="45">
         <v>0.5</v>
       </c>
-      <c r="D39" s="48">
+      <c r="D39" s="45">
         <v>1</v>
       </c>
-      <c r="E39" s="48" t="s">
-        <v>137</v>
+      <c r="E39" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="48">
+        <v>134</v>
+      </c>
+      <c r="B40" s="45">
         <v>0.5</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="45">
         <v>1.5</v>
       </c>
-      <c r="D40" s="48">
+      <c r="D40" s="45">
         <v>3</v>
       </c>
-      <c r="E40" s="48" t="s">
-        <v>139</v>
+      <c r="E40" s="45" t="s">
+        <v>135</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="38"/>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
       <c r="F41" s="38"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="38"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
       <c r="F42" s="38"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="38" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B47" s="40">
         <v>10000</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="38" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B48" s="40">
         <v>42</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="38" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B49" s="40">
         <v>0</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -6250,12 +6238,12 @@
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -6263,13 +6251,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>77</v>
@@ -6280,7 +6268,7 @@
     </row>
     <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B63" s="42">
         <v>1</v>
@@ -6292,10 +6280,10 @@
         <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F63" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -6316,30 +6304,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="A1" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="A2" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D4" s="37" t="s">
         <v>78</v>
@@ -6347,139 +6335,139 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="38" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B5" s="40">
         <v>330</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="38" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B6" s="40">
         <v>0.8</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="38" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B7" s="40">
         <v>0.5</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="38" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B8" s="40">
         <v>0.75</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B9" s="40">
         <v>7</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="38" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B10" s="40">
         <v>0</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="38" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B11" s="40">
         <v>1000</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="38" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B12" s="40">
         <v>24</v>
       </c>
       <c r="C12" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
